--- a/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
+++ b/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
@@ -590,6 +590,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -604,6 +605,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -652,7 +654,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>All 18 rows opened by the 2026-08-25 meeting have now been answered. DECISION G (G1-G6) resolved to a PRESENTATION-ONLY +30% uplift — the ceiling and the AIP→WFP limit both see the BASE figure. A6-1's all-fund ceiling was REVERSED BACK to General Fund only (A1-b, A6-4, confirmed 2026-08-26), so A6-1 is superseded, A6-4 is N/A and work item V18-78 is dropped. Three rows are HELD OPEN because the answer does not pick between the options asked (G5, A5-b, A1-b), and four follow-up rows were added (B9-b, B10-b, B12-b, W13-b). The reading of each answer is in Phase_Plan.md §12.</t>
+          <t>All 18 rows opened by the 2026-08-25 meeting have now been answered. DECISION G (G1-G6) resolved to a PRESENTATION-ONLY +30% uplift — the ceiling and the AIP→WFP limit both see the BASE figure. A6-1's all-fund ceiling was REVERSED BACK to General Fund only (A1-b, A6-4, confirmed 2026-08-26), so A6-1 is superseded, A6-4 is N/A and work item V18-78 is dropped. Three rows are HELD OPEN because the answer does not pick between the options asked (G5, A5-b, A1-b), and four follow-up rows were added (B9-b, B10-b, B12-b, W13-b). The reading of each answer is in Phase_Plan.md §12. A1-b was closed later the same day: the WFP allocation check STAYS LIVE (it was going to be retired), an expenditure is bound by the LESSER of its AIP activity and the fund's current remaining allocation, and the AIP reservation is relieved per activity as the WFP commits. NO BLOCKER REMAINS.</t>
         </is>
       </c>
     </row>
@@ -3437,8 +3439,9 @@
         <is>
           <t>I think yes.
 But in a later discussion, we will go back to old requirement where only GF will have ceiling check. Sorry
-✅ The GF-only half is CONFIRMED (2026-08-26) and is recorded in A6-1 / A6-4.
-⚠️ The blocking half is HELD OPEN — "I think yes" (retire WFP's own allocation draw-down for FY2028+) is not firm enough to ticket V18-45 / V18-46 on. Without it the same peso is drawn down twice. Confirm before Phase 2.</t>
+[2026-08-26] "Mostly correct — but it may be possible that fund allocation will be different during WFP creation." Clarified: BOTH the allocation AMOUNT and the FUND MIX may differ by WFP time, and the WFP is limited by THE LESSER of the AIP activity and the current allocation.
+✅ SETTLED. The WFP allocation check is NOT retired — retiring it would hide exactly the change Ralph is describing. It stays live and validates per fund against the allocation AS IT STANDS AT WFP TIME. An expenditure must satisfy both bounds: &lt;= its AIP activity amount, and &lt;= the fund's currently remaining allocation. A raised allocation gives no extra room without amending the AIP (V18-73); a cut allocation blocks the difference.
+⚠️ No double-count: the AIP row is a RESERVATION that the WFP RELIEVES as it commits. Allocation consumed = WFP committed + AIP reserved not yet converted. Relief must be PER ACTIVITY, not per fund — relieving per fund strands reservations whenever the fund mix changes. Written out in Phase_Plan §12.1.</t>
         </is>
       </c>
       <c r="I42" s="15" t="inlineStr">
@@ -3447,11 +3450,11 @@
         </is>
       </c>
       <c r="J42" s="16" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="K42" s="15" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="L42" s="13" t="inlineStr">
@@ -4367,7 +4370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5214,7 +5217,34 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>The AIP/WFP double-count (DECISION A, second half)</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>The WFP allocation check STAYS LIVE for FY2028+ — it is not retired, because the allocation may differ in AMOUNT and in FUND MIX by the time the WFP is written. A WFP expenditure is bound by THE LESSER of its AIP activity amount and the fund's currently remaining allocation. The AIP row is a reservation that the WFP relieves PER ACTIVITY as it commits, so the two ledgers net rather than add. Overturns the plan's own recommendation to retire the check.</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Ralph</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Phase_Plan §12.1 / V18-45, V18-46</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Recorded here so nobody re-opens them by accident. If one of these is reversed, it needs changing in the source documents too — not only here.</t>
         </is>

--- a/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
+++ b/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
@@ -590,7 +590,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -605,7 +604,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -850,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2637,7 +2635,8 @@
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>Ask for a FILLED-IN copy of whatever they use today, not a description. On the WFP export the "template" we were given turned out to be a filled sample, and the difference cost real time.</t>
+          <t>Ask for a FILLED-IN copy of whatever they use today, not a description. On the WFP export the "template" we were given turned out to be a filled sample, and the difference cost real time.
+[2026-08-26] Ask PBO and GSO SEPARATELY. The WFP document is needed by PBO; GSO only built the system that generates it. The office that NEEDS the output and the office that MAKES the tool are different, and they may not give the same answer.</t>
         </is>
       </c>
       <c r="H29" s="15" t="n"/>
@@ -2668,7 +2667,8 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>GSO specifically: is the read-only AIP API already designed for you a better fit than a file export? A live connection never goes stale.</t>
+          <t>GSO specifically: is the read-only AIP API already designed for you a better fit than a file export? A live connection never goes stale.
+[2026-08-26] RE-RATED BLOCKER. New context from Ralph: the FY2028 WFP may not be built in this system at all — the approved AIP may be sent to GSO, whose system built the FY2027 WFP for other offices. (The WFP document itself is needed by PBO; GSO only builds the tool.) So this question now decides whether our AIP is the END of the chain or a FEED into someone else's, which is why it stopped being a Phase 5 nicety.</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
@@ -2678,17 +2678,18 @@
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Blocker</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>Phase 5 outputs</t>
+          <t>Phase 5 outputs — AND, since 2026-08-26, the FY2028 WFP path (V18-81, V18-45)</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>Ask before building a file export — docs/External_AIP_API_Contract.md is already written and sitting in the backlog.</t>
+          <t>Ask before building a file export — docs/External_AIP_API_Contract.md is already written and sitting in the backlog, and its open item #4 already asks GSO "anything missing for WFP BUILDING (e.g. account-level breakdown beyond PS/MOOE/CO totals)?". Half-scoped already.
+⚠️ Raise one thing explicitly: the old format's "AIP data carries no per-fund breakdown" (WfpCeilingService §2 D3) is a FY&lt;=2027 constraint. The new format puts ONE FUND SOURCE PER EXPENSE LINE, so the FY2028 export CAN carry the per-fund detail GSO needs to do allocation checking on their side. If GSO cannot see funds either, the fund-mix problem does not disappear — it relocates to a system with LESS information than this one.</t>
         </is>
       </c>
       <c r="H30" s="15" t="n"/>
@@ -4341,6 +4342,108 @@
         </is>
       </c>
       <c r="M57" s="13" t="n"/>
+    </row>
+    <row r="58" ht="156.6" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>B. PPDC</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>After the PPDO reviewers approve the consolidated AIP, Ralph's understanding is that it is presented to the Sangguniang Panlalawigan (SP) — the elected board members and the Vice Governor — who review it and pass a RESOLUTION approving it. Is that stage represented in this system at all: a state beyond Consolidated, a record of the resolution, a document generated for the SP? And who marks it approved?</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>PPDC / Ralph</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="inlineStr">
+        <is>
+          <t>V18-73 (amendment readiness), the Phase 4 state machine, Phase 5 outputs</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>Recorded as Ralph's understanding, not as a confirmed requirement — he hedged it ("I think") several times, so confirm before building on it. It matters because the plan currently treats PPDO consolidation as the end of the ladder, and if the SP resolution is the real terminal authority then "approved" means something this system does not yet model. The cheapest correct version is probably a state plus a resolution reference, with the SP itself staying offline.</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n"/>
+      <c r="I58" s="15" t="n"/>
+      <c r="J58" s="16" t="n"/>
+      <c r="K58" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L58" s="13" t="inlineStr">
+        <is>
+          <t>Phase_Plan §12.6</t>
+        </is>
+      </c>
+      <c r="M58" s="13" t="n"/>
+    </row>
+    <row r="59" ht="156.6" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>B. PPDC</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>Supplemental / amendment changes to an approved AIP: Ralph's understanding is that these go to the SP for approval FIRST, before taking effect. Does that mean an amendment is a second full trip through review and resolution, or something lighter?</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>PPDC / Ralph</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="inlineStr">
+        <is>
+          <t>V18-73 / RAL-78 — amendment readiness</t>
+        </is>
+      </c>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>This makes V18-73 a workflow question before it is a schema one. Its note still reads "don't make LFC approval terminal", which is now doubly stale — the LFC is out of the system, and the terminal authority appears to be the SP resolution instead.</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n"/>
+      <c r="I59" s="15" t="n"/>
+      <c r="J59" s="16" t="n"/>
+      <c r="K59" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L59" s="13" t="inlineStr">
+        <is>
+          <t>Phase_Plan §12.6 / V18-73</t>
+        </is>
+      </c>
+      <c r="M59" s="13" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L53">
@@ -4370,7 +4473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5244,7 +5347,34 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>FY2028 WFP — what gets built (amends the row above)</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>WfpCeilingService is left UNTOUCHED (zero diff) — not retired, not made conditional. Retiring the allocation check for FY2028+ would ADD four fiscal-year conditionals rather than delete code, and it is inert anyway if no FY2028 WFP is created here. What IS deferred is the new work: V18-45 becomes an AIP-ONLY reservation ledger with NO relief/netting mechanism, and V18-81 blocks FY2028+ WFP creation in this system as "not supported yet" — making the double-count impossible rather than silently wrong. Reason: the FY2028 WFP may be built in GSO's system instead. Tracker C2 re-rated Blocker.</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Ralph</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Phase_Plan §12.1 / V18-45, V18-81</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Recorded here so nobody re-opens them by accident. If one of these is reversed, it needs changing in the source documents too — not only here.</t>
         </is>

--- a/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
+++ b/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Settled" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open Items'!$A$1:$L$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open Items'!$A$1:$L$59</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Open Items'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2636,7 +2636,8 @@
       <c r="G29" s="13" t="inlineStr">
         <is>
           <t>Ask for a FILLED-IN copy of whatever they use today, not a description. On the WFP export the "template" we were given turned out to be a filled sample, and the difference cost real time.
-[2026-08-26] Ask PBO and GSO SEPARATELY. The WFP document is needed by PBO; GSO only built the system that generates it. The office that NEEDS the output and the office that MAKES the tool are different, and they may not give the same answer.</t>
+[2026-08-26] Ask PBO and GSO SEPARATELY. The WFP document is needed by PBO; GSO only built the system that generates it. The office that NEEDS the output and the office that MAKES the tool are different, and they may not give the same answer.
+[2026-08-26] Same sequencing as C2: the new AIP structure comes first, then the conversation.</t>
         </is>
       </c>
       <c r="H29" s="15" t="n"/>
@@ -2678,18 +2679,20 @@
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>Blocker</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>Phase 5 outputs — AND, since 2026-08-26, the FY2028 WFP path (V18-81, V18-45)</t>
+          <t>Phase 5 outputs; the FY2028 WFP path (V18-81, V18-45) when it resumes</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
           <t>Ask before building a file export — docs/External_AIP_API_Contract.md is already written and sitting in the backlog, and its open item #4 already asks GSO "anything missing for WFP BUILDING (e.g. account-level breakdown beyond PS/MOOE/CO totals)?". Half-scoped already.
-⚠️ Raise one thing explicitly: the old format's "AIP data carries no per-fund breakdown" (WfpCeilingService §2 D3) is a FY&lt;=2027 constraint. The new format puts ONE FUND SOURCE PER EXPENSE LINE, so the FY2028 export CAN carry the per-fund detail GSO needs to do allocation checking on their side. If GSO cannot see funds either, the fund-mix problem does not disappear — it relocates to a system with LESS information than this one.</t>
+⚠️ Raise one thing explicitly: the old format's "AIP data carries no per-fund breakdown" (WfpCeilingService §2 D3) is a FY&lt;=2027 constraint. The new format puts ONE FUND SOURCE PER EXPENSE LINE, so the FY2028 export CAN carry the per-fund detail GSO needs to do allocation checking on their side. If GSO cannot see funds either, the fund-mix problem does not disappear — it relocates to a system with LESS information than this one.
+[2026-08-26] SEQUENCING DECIDED (Ralph): "I will leave C1 and C2 as-is for now since we haven't had a discussion yet with GSO — and I would prefer if we already have the structure of our new AIP that can be provided to them." So: BUILD THE AIP STRUCTURE FIRST, then engage GSO with something concrete. Kept at High rather than escalated to Blocker — a Blocker nobody intends to unblock is noise.
+⚠️ This deferral is only safe because of V18-81 (FY2028+ WFP creation blocked in this system). With it, deferring GSO can only produce a MISSING FEATURE; without it, the same deferral would leave the double-count question open while Phases 2-3 are built on top of it.</t>
         </is>
       </c>
       <c r="H30" s="15" t="n"/>
@@ -3009,7 +3012,7 @@
       </c>
       <c r="M35" s="13" t="n"/>
     </row>
-    <row r="36" ht="87" customHeight="1">
+    <row r="36" hidden="1" ht="87" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
           <t>G1</t>
@@ -3074,7 +3077,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="104.4" customHeight="1">
+    <row r="37" hidden="1" ht="104.4" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
           <t>G2</t>
@@ -3139,7 +3142,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="87" customHeight="1">
+    <row r="38" hidden="1" ht="87" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
           <t>G3</t>
@@ -3204,7 +3207,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="69.59999999999999" customHeight="1">
+    <row r="39" hidden="1" ht="69.59999999999999" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
           <t>G4</t>
@@ -3307,7 +3310,7 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Yes
+          <t>Yes, Uplift, then round
 ⚠️ HELD OPEN 2026-08-26 — the question was an either/or (uplift-then-round, or round-then-uplift), so a bare "Yes" does not pick one. Read as UPLIFT, THEN ROUND (the recommendation). One word confirms it.</t>
         </is>
       </c>
@@ -3317,7 +3320,7 @@
         </is>
       </c>
       <c r="J40" s="16" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="K40" s="15" t="inlineStr">
         <is>
@@ -3335,7 +3338,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="87" customHeight="1">
+    <row r="41" hidden="1" ht="87" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
           <t>G6</t>
@@ -3400,7 +3403,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="121.8" customHeight="1">
+    <row r="42" hidden="1" ht="121.8" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
           <t>A1-b</t>
@@ -3507,7 +3510,7 @@
       </c>
       <c r="H43" s="15" t="inlineStr">
         <is>
-          <t>yes
+          <t>yes, let follow the recommendation
 ⚠️ HELD OPEN 2026-08-26 — the question was "what happens", not yes/no. Read as the recommendation: the encoded work STANDS and simply fails at submit, consistent with DECISION C. Confirm.</t>
         </is>
       </c>
@@ -3517,7 +3520,7 @@
         </is>
       </c>
       <c r="J43" s="16" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="K43" s="15" t="inlineStr">
         <is>
@@ -3535,7 +3538,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="69.59999999999999" customHeight="1">
+    <row r="44" hidden="1" ht="69.59999999999999" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
           <t>A6-4</t>
@@ -3601,7 +3604,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="104.4" customHeight="1">
+    <row r="45" hidden="1" ht="104.4" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
           <t>B9</t>
@@ -3666,7 +3669,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="348" customHeight="1">
+    <row r="46" hidden="1" ht="348" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
           <t>B10</t>
@@ -3728,7 +3731,7 @@
       </c>
       <c r="M46" s="13" t="n"/>
     </row>
-    <row r="47" ht="156.6" customHeight="1">
+    <row r="47" hidden="1" ht="156.6" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
           <t>B11</t>
@@ -3789,7 +3792,7 @@
       </c>
       <c r="M47" s="13" t="n"/>
     </row>
-    <row r="48" ht="69.59999999999999" customHeight="1">
+    <row r="48" hidden="1" ht="69.59999999999999" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
           <t>B12</t>
@@ -3850,7 +3853,7 @@
       </c>
       <c r="M48" s="13" t="n"/>
     </row>
-    <row r="49" ht="156.6" customHeight="1">
+    <row r="49" hidden="1" ht="156.6" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
           <t>B13</t>
@@ -3911,7 +3914,7 @@
       </c>
       <c r="M49" s="13" t="n"/>
     </row>
-    <row r="50" ht="69.59999999999999" customHeight="1">
+    <row r="50" hidden="1" ht="69.59999999999999" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
           <t>W10</t>
@@ -3968,7 +3971,7 @@
       </c>
       <c r="M50" s="13" t="n"/>
     </row>
-    <row r="51" ht="69.59999999999999" customHeight="1">
+    <row r="51" hidden="1" ht="69.59999999999999" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
           <t>W11</t>
@@ -4025,7 +4028,7 @@
       </c>
       <c r="M51" s="13" t="n"/>
     </row>
-    <row r="52" ht="87" customHeight="1">
+    <row r="52" hidden="1" ht="87" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
           <t>W12</t>
@@ -4082,7 +4085,7 @@
       </c>
       <c r="M52" s="13" t="n"/>
     </row>
-    <row r="53" ht="174" customHeight="1">
+    <row r="53" hidden="1" ht="174" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
           <t>W13</t>
@@ -4175,12 +4178,36 @@
           <t>Reading to confirm: segments 1-5 are the sector + office code, segments 6/7/8 are the program / project / activity sequences. Indexed columns need a defined MAXIMUM depth before they can be created — a variable-length code cannot be split into fixed columns without one. Retrofitting means migrating every AIP row.</t>
         </is>
       </c>
-      <c r="H54" s="15" t="n"/>
-      <c r="I54" s="15" t="n"/>
-      <c r="J54" s="16" t="n"/>
+      <c r="H54" s="15" t="inlineStr">
+        <is>
+          <t>✅ ANSWERED from the primary source. DBM Budget Operations Manual for LGUs, 2023 Edition (2024 reprint) — Figure 4 "AIP Reference Code Guide" (printed p.25), Annex C (sectors), Annex D (LGU level / office type / office).
+The layout is PRESCRIBED, not LGU-invented:
+  seg 1  Sector       4 digits  1000 General Public Services / 3000 Social Services / 8000 Economic Services / 9000 Other Services
+  seg 2  Sub-Sector   3 digits  "if any" — Annex C sub-groups, in practice mainly Social Services
+  seg 3  LGU Level    1 digit   1 Province / 2 City / 3 Municipality
+  seg 4  Office Type  2 digits  01 Mandatory / 02 Optional / 03 Others
+  seg 5  Office       3 digits  Annex D lists 001-022 per level+type; "03 Others" is left unenumerated for the LGU to assign
+  seg 6+ PPA path     3 each    Program &gt; Project &gt; Activity — ONE SEGMENT PER LEVEL
+Verified against all three real codes:
+• 8000-000-1-01-010-001 (our LDIP seed) = Economic / — / Province / Mandatory / 010 = Office of the Provincial Planning and Development Coordinator (PPDO itself) / Program 001
+• 8000-000-1-03-009-001-001-001 (Ralph's) = … / OTHERS / office 009 — LGU-assigned, which is why it is not in Annex D / Program-Project-Activity
+• 8000-000-1-01-016-004-001-003-001 (.xlsm parser test) = … / 016 = Office of the Provincial Agriculturist / a FOUR-segment PPA path
+WHERE SEQUENCES RESET: the manual requires that "all activities and projects be subsumed under a specific program" (p.26), so the PPA path is a tree — program numbered within its office, project within its program, activity within its project.
+⚠️ STILL TO CONFIRM (minor): does the PROGRAM sequence restart each fiscal year, or run continuously? The v1.3 LDIP work numbered programs continuously across sub-office groups.
+⚠️ THIS RESHAPES V18-76 and removes the blocker this row raised. Segments 1-5 are FIXED — five indexed columns, pure office identity. Segments 6+ are a VARIABLE-LENGTH path and must NOT be columns: give each Program/Project/Activity node a sibling-unique seq and RENDER the code from the root-to-node path. There is no maximum depth, and none is needed.</t>
+        </is>
+      </c>
+      <c r="I54" s="15" t="inlineStr">
+        <is>
+          <t>Ralph (source) / read from the BOM</t>
+        </is>
+      </c>
+      <c r="J54" s="16" t="n">
+        <v>46260</v>
+      </c>
       <c r="K54" s="15" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="L54" s="13" t="inlineStr">
@@ -4379,9 +4406,25 @@
           <t>Recorded as Ralph's understanding, not as a confirmed requirement — he hedged it ("I think") several times, so confirm before building on it. It matters because the plan currently treats PPDO consolidation as the end of the ladder, and if the SP resolution is the real terminal authority then "approved" means something this system does not yet model. The cheapest correct version is probably a state plus a resolution reference, with the SP itself staying offline.</t>
         </is>
       </c>
-      <c r="H58" s="15" t="n"/>
-      <c r="I58" s="15" t="n"/>
-      <c r="J58" s="16" t="n"/>
+      <c r="H58" s="15" t="inlineStr">
+        <is>
+          <t>✅ CONFIRMED by the BOM (printed pp.23-24) — this is statutory, not local practice. AND it adds a stage Ralph did not mention:
+• Preparation and/or APPROVAL of the AIP by the LOCAL DEVELOPMENT COUNCIL (LDC) — SLPBC 2016 puts AIP preparation within the month of MAY.
+• Submission of the LDC-approved AIP to the Sanggunian — reasonable time prior to JUNE 7.
+• Approval of the AIP by the Sanggunian — on or before JUNE 7 (DILG-NEDA-DBM-DOF JMC No. 1, s. 2016).
+So the chain downstream of PPDO is PPDO &gt; LDC &gt; SANGGUNIAN — TWO external bodies, not one.
+⚠️ STILL OPEN, and this is the actual question: is either stage represented in this system (a state beyond Consolidated, a resolution reference, a document generated for the LDC/SP), or do both stay entirely offline with someone marking the result? Cheapest correct version is probably a state plus a resolution reference, with both bodies staying offline.
+ℹ️ No conflict with B7 ("no deadline in the system"): B7 is about offices submitting to PPDO, which is internal. June 7 is statutory and applies to the Sanggunian step.</t>
+        </is>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
+        <is>
+          <t>BOM (partial) — modelling question still open</t>
+        </is>
+      </c>
+      <c r="J58" s="16" t="n">
+        <v>46260</v>
+      </c>
       <c r="K58" s="15" t="inlineStr">
         <is>
           <t>Open</t>
@@ -4389,7 +4432,7 @@
       </c>
       <c r="L58" s="13" t="inlineStr">
         <is>
-          <t>Phase_Plan §12.6</t>
+          <t>Phase_Plan §12.6 / BOM pp.23-24</t>
         </is>
       </c>
       <c r="M58" s="13" t="n"/>
@@ -4446,7 +4489,7 @@
       <c r="M59" s="13" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L53">
+  <autoFilter ref="A1:L59">
     <filterColumn colId="10" hiddenButton="0" showButton="1">
       <filters>
         <filter val="Open"/>
@@ -5157,7 +5200,7 @@
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="52.8" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Reviewer powers split in two</t>
@@ -5184,7 +5227,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="52.8" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>One reviewer per office — how it is enforced</t>
@@ -5211,7 +5254,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="52.8" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>PPDO's own internal submit path</t>
@@ -5238,7 +5281,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="39.6" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>AIP ref-code format</t>
@@ -5265,7 +5308,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="39.6" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Price Index feeds AIP costing</t>
@@ -5319,7 +5362,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="79.2" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>The AIP/WFP double-count (DECISION A, second half)</t>
@@ -5346,7 +5389,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="105.6" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>FY2028 WFP — what gets built (amends the row above)</t>

--- a/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
+++ b/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
@@ -4383,7 +4383,7 @@
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>After the PPDO reviewers approve the consolidated AIP, Ralph's understanding is that it is presented to the Sangguniang Panlalawigan (SP) — the elected board members and the Vice Governor — who review it and pass a RESOLUTION approving it. Is that stage represented in this system at all: a state beyond Consolidated, a record of the resolution, a document generated for the SP? And who marks it approved?</t>
+          <t>After the PPDO reviewers approve the consolidated AIP, Ralph's understanding is that it is presented to the PDC (Provincial Development Council) and then to the Sangguniang Panlalawigan (SP) — the elected board members and the Vice Governor — who review it and pass a RESOLUTION approving it. Is that stage represented in this system at all: a state beyond Consolidated, a record of the resolution, a document generated for the SP? And who marks it approved?</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr">
@@ -4414,7 +4414,11 @@
 • Approval of the AIP by the Sanggunian — on or before JUNE 7 (DILG-NEDA-DBM-DOF JMC No. 1, s. 2016).
 So the chain downstream of PPDO is PPDO &gt; LDC &gt; SANGGUNIAN — TWO external bodies, not one.
 ⚠️ STILL OPEN, and this is the actual question: is either stage represented in this system (a state beyond Consolidated, a resolution reference, a document generated for the LDC/SP), or do both stay entirely offline with someone marking the result? Cheapest correct version is probably a state plus a resolution reference, with both bodies staying offline.
-ℹ️ No conflict with B7 ("no deadline in the system"): B7 is about offices submitting to PPDO, which is internal. June 7 is statutory and applies to the Sanggunian step.</t>
+ℹ️ No conflict with B7 ("no deadline in the system"): B7 is about offices submitting to PPDO, which is internal. June 7 is statutory and applies to the Sanggunian step.
+[2026-08-26, Ralph] CONFIRMED, and the LDC is named: "For our case the LDC is the PDC (Provincial Development Council). The AIP generated by our portal/application will be presented there, then in the Sanggunian."
+✅ That settles the GENERATION half — both bodies are OFFLINE as far as this system is concerned, and what they consume is a document we produce (V18-60).
+⚠️ STILL OPEN, and now this is the whole of B14: does the system RECORD THE OUTCOME — a state beyond Consolidated, a resolution reference, a return-for-revision path from PDC or SP — or does someone simply report back and no state changes? (B15 is the same question for supplementals.)
+⚠️ Consequence for V18-60: the official AIP form is presented to the PDC and then to elected officials under a June 7 statutory deadline — not an internal report. It is also where the +30% uplift first meets readers who did not encode it, including the ceiling-exceedance DECISION G deliberately permits, so the form or its covering note must say so.</t>
         </is>
       </c>
       <c r="I58" s="15" t="inlineStr">

--- a/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
+++ b/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
@@ -848,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4491,6 +4491,57 @@
         </is>
       </c>
       <c r="M59" s="13" t="n"/>
+    </row>
+    <row r="60" ht="156.6" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>E. +30% uplift</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>Does the +30% show in the MOOE and CO COLUMNS themselves, or only in the Total column? G6 settled that the printed Total is PS + 1.3 x (MOOE + CO), but column O on the official form is labelled "8+9+10" and every total in the province's file is a SUM of the cells beside or below it.</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>PBO / PPDC</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>Blocker</t>
+        </is>
+      </c>
+      <c r="F60" s="13" t="inlineStr">
+        <is>
+          <t>V18-60 — the printable AIP form cannot be built without it</t>
+        </is>
+      </c>
+      <c r="G60" s="13" t="inlineStr">
+        <is>
+          <t>Uplift M and N themselves. It is the only reading under which BOTH G6 and DECISION 9 hold: O = SUM(L:N) keeps working AND equals PS + 1.3 x (MOOE + CO). If M and N print base values instead, then L + M + N &lt;&gt; O on every row with MOOE or CO — the row visibly does not add up and column O contradicts its own printed label, in a document read by elected officials at the PDC and the Sanggunian.</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n"/>
+      <c r="I60" s="15" t="n"/>
+      <c r="J60" s="16" t="n"/>
+      <c r="K60" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L60" s="13" t="inlineStr">
+        <is>
+          <t>AIP_Form_Spec.md §6.1</t>
+        </is>
+      </c>
+      <c r="M60" s="13" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L59">

--- a/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
+++ b/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
@@ -3311,7 +3311,8 @@
       <c r="H40" s="15" t="inlineStr">
         <is>
           <t>Yes, Uplift, then round
-⚠️ HELD OPEN 2026-08-26 — the question was an either/or (uplift-then-round, or round-then-uplift), so a bare "Yes" does not pick one. Read as UPLIFT, THEN ROUND (the recommendation). One word confirms it.</t>
+⚠️ HELD OPEN 2026-08-26 — the question was an either/or (uplift-then-round, or round-then-uplift), so a bare "Yes" does not pick one. Read as UPLIFT, THEN ROUND (the recommendation). One word confirms it.
+[2026-08-26] Slightly more load-bearing since G7. With M and N printing uplifted, G5 decides the exact figure in the money columns of a document presented to the PDC and the Sanggunian — ₱1,000,400 base prints as 1,301 (uplift-then-round) or 1,302 (round-then-uplift). Still just a one-word confirmation.</t>
         </is>
       </c>
       <c r="I40" s="15" t="inlineStr">
@@ -4528,12 +4529,25 @@
           <t>Uplift M and N themselves. It is the only reading under which BOTH G6 and DECISION 9 hold: O = SUM(L:N) keeps working AND equals PS + 1.3 x (MOOE + CO). If M and N print base values instead, then L + M + N &lt;&gt; O on every row with MOOE or CO — the row visibly does not add up and column O contradicts its own printed label, in a document read by elected officials at the PDC and the Sanggunian.</t>
         </is>
       </c>
-      <c r="H60" s="15" t="n"/>
-      <c r="I60" s="15" t="n"/>
-      <c r="J60" s="16" t="n"/>
+      <c r="H60" s="15" t="inlineStr">
+        <is>
+          <t>✅ M AND N UPLIFTED — the MOOE and CO columns themselves carry the +30%, not only the Total. Ralph raised this scenario with PPDC directly and this is what will be followed: "as long as the entered value (in round up) follows the ceiling."
+So O = SUM(L:N) still holds AND equals PS + 1.3 x (MOOE + CO) at the same time — G6 and DECISION 9 are both satisfied, and the row visibly adds up.
+✅ The qualifier corroborates G3 and A2-4 together: the ceiling is compared against the ENTERED figures ROUNDED UP — base, rounded. Two numbers exist by design: base MOOE+CO (rounded) for the ceiling check, uplifted MOOE+CO for the printed columns.
+⚠️ DO NOT assume printed = 1.3 x checked. Before rounding the ratio is exactly 1.3; after rounding it is not, and by how much depends on G5 (still open). Example: ₱1,000,400 base → ceiling sees 1,001; the form shows 1,301 under uplift-then-round or 1,302 under round-then-uplift. No test or reconciliation should assert that ratio.</t>
+        </is>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
+        <is>
+          <t>Ralph, PPDC</t>
+        </is>
+      </c>
+      <c r="J60" s="16" t="n">
+        <v>46260</v>
+      </c>
       <c r="K60" s="15" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="L60" s="13" t="inlineStr">

--- a/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
+++ b/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
@@ -3310,9 +3310,10 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Yes, Uplift, then round
-⚠️ HELD OPEN 2026-08-26 — the question was an either/or (uplift-then-round, or round-then-uplift), so a bare "Yes" does not pick one. Read as UPLIFT, THEN ROUND (the recommendation). One word confirms it.
-[2026-08-26] Slightly more load-bearing since G7. With M and N printing uplifted, G5 decides the exact figure in the money columns of a document presented to the PDC and the Sanggunian — ₱1,000,400 base prints as 1,301 (uplift-then-round) or 1,302 (round-then-uplift). Still just a one-word confirmation.</t>
+          <t>Yes
+✅ RESOLVED 2026-08-26. Asked concretely (₱1,000,400 base prints as 1,301 or 1,302?), Ralph answered 1,301 — which is UPLIFT, THEN ROUND. ₱1,000,400 x 1.3 = ₱1,300,520, rounded up to the thousand = 1,301. (Round-then-uplift would give 1,001 x 1.3 = 1,301.3 → 1,302.)
+Matches the original recommendation: rounding first would round a number nobody ever sees.
+⚠️ Applies to the printed columns M and N and to O. The CEILING check is separate and unaffected — it compares the entered base, rounded up (G3 / A2-4 / G7).</t>
         </is>
       </c>
       <c r="I40" s="15" t="inlineStr">
@@ -3325,7 +3326,7 @@
       </c>
       <c r="K40" s="15" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="L40" s="13" t="inlineStr">
@@ -3511,8 +3512,10 @@
       </c>
       <c r="H43" s="15" t="inlineStr">
         <is>
-          <t>yes, let follow the recommendation
-⚠️ HELD OPEN 2026-08-26 — the question was "what happens", not yes/no. Read as the recommendation: the encoded work STANDS and simply fails at submit, consistent with DECISION C. Confirm.</t>
+          <t>yes
+✅ CONFIRMED 2026-08-26: the encoded work STANDS and fails at submit. Nothing is deleted, adjusted or flagged at the moment PBO cuts the ceiling. Consistent with DECISION C (block at submit, not at save), and it avoids destroying work the office did in good faith.
+⚠️ IMPLEMENTATION TRAP for V18-48/V18-45: after a cut, an office's REMAINING allocation is legitimately NEGATIVE — and that is exactly the state that must block submit. A Math.Max(0, ...) anywhere in the ledger, the DTO or the UI would hide the only signal the office has that it is over. Show the negative figure.
+ℹ️ Scope: this covers a cut while the office is still ENCODING. A ceiling cut AFTER the AIP is approved is a different path — that is the supplemental/amendment route through the PDC and Sanggunian (tracker B15 / V18-73), not this row.</t>
         </is>
       </c>
       <c r="I43" s="15" t="inlineStr">
@@ -3525,7 +3528,7 @@
       </c>
       <c r="K43" s="15" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="L43" s="13" t="inlineStr">
@@ -4282,7 +4285,9 @@
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>B12 confirmed PPDO's divisions submit to a PPDO department-head reviewer, distinct from the consolidated reviewer. Underneath it the record SHAPE is still unstated: one AIP record per PPDO division, or one PPDO record with division-tagged rows?</t>
+          <t>PPDO's divisions and the AIP record shape.
+[REFRAMED 2026-08-26 after reading the province's FY2027 file and the existing entities — the original either/or was the wrong question.]
+THE ONE QUESTION FOR PPDC: on the PRINTED AIP, does each PPDO division appear as its own office row — the way "OFFICE OF THE GOVERNOR - HOUSING" and "OFFICE OF THE GOVERNOR - AKAP-HUB" do today — e.g. "PROVINCIAL PLANNING AND DEVELOPMENT OFFICE - PLANNING"? Or do all PPDO divisions encode into the same PPDO office rows, with the division being purely internal and never printed?</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
@@ -4297,12 +4302,22 @@
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>V18-55, V18-40 — the last structural unknown in Phase 4</t>
+          <t>V18-40 (Phase 2 — record shape), V18-55, V18-11</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>"Mirroring an office" implies one record per division, and "PPDO encoders see only their division's work" is satisfied by either shape. It has to be said explicitly — it decides whether the consolidated document holds ~20 rows or ~25.</t>
+          <t>✅ THE STORAGE SHAPE NO LONGER NEEDS ASKING — it is settled by existing practice and existing code. The original either/or (one record per PPDO division vs one record with division-tagged rows) posed a choice the system already made:
+• In the province's FY2027 file, an office appears MULTIPLE times as separate office rows sharing one office ref code, distinguished by a NAME SUFFIX, and split across sectors. The Governor's Office appears 8 times across 3 sectors (- WARDEN, - AKAP-HUB, - HOUSING, - LOCAL SCHOOL BOARD, - TOURISM, - ABE, - PCDO). PPDO itself appears TWICE (GENERAL, and ECONOMIC as "- SPECIAL").
+• AipOffice and LdipOffice ALREADY implement this. LdipOffice's own doc comment: "A sector may hold MULTIPLE groups sharing that same ref code, distinguished by Name … Group identity within a record is the (Sector, Name) pair."
+• Program sequences already run CONTINUOUSLY across those groups (RAL-61), so there is no ref-code collision to design around.
+So: one AIP record per office; a sub-unit is its own AipOffice row. Neither original option.
+WHAT ACTUALLY REMAINS is whether a PPDO division IS one of those sub-office groups, which is what the question above asks, and it has a visible consequence PPDC can judge: whether the printed AIP shows PPDO as one block or several.
+RECOMMENDATION — yes, divisions are sub-office groups, and AipOffice gains a nullable division_id FK (null for ordinary offices, set for the host office's rows):
+• Reuses a mechanism that exists and matches how the province really encodes.
+• Turns "PPDO encoders see only their division's work" (B12) into a COLUMN rather than a name-string convention — exactly V18-11's point about string keys becoming load-bearing.
+• Per-division submit state hangs off the sub-group row naturally, which is what B12's "PPDO divisions submit to a PPDO department-head reviewer" needs.
+⚠️ If the answer is NO (divisions never print), the division tag must live somewhere that never reaches the form, and B12's per-division scoping and per-division submit both need a different mechanism — more work, not less.</t>
         </is>
       </c>
       <c r="H56" s="15" t="n"/>
@@ -4315,7 +4330,7 @@
       </c>
       <c r="L56" s="13" t="inlineStr">
         <is>
-          <t>AIP_Redesign_Notes §4 Q2 / tracker B12</t>
+          <t>Phase_Plan §12.6 / AipOffice + LdipOffice / FY2027 file</t>
         </is>
       </c>
       <c r="M56" s="13" t="n"/>
@@ -4935,7 +4950,8 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Division allocations may total LESS than the office ceiling. (What happens when a ceiling is cut after encoding is still open - tracker A5-b.)</t>
+          <t>Division allocations may total LESS than the office ceiling (they may never exceed it).
+✅ Second half answered 2026-08-26 (A5-b): when PBO CUTS a ceiling after divisions have encoded against it, the encoded work STANDS and fails at submit. Non-destructive; no cascade. ⚠️ Remaining allocation goes legitimately negative — do not clamp it at zero.</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4945,7 +4961,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-25, completed 2026-08-26</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">

--- a/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
+++ b/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
@@ -4320,12 +4320,29 @@
 ⚠️ If the answer is NO (divisions never print), the division tag must live somewhere that never reaches the form, and B12's per-division scoping and per-division submit both need a different mechanism — more work, not less.</t>
         </is>
       </c>
-      <c r="H56" s="15" t="n"/>
-      <c r="I56" s="15" t="n"/>
-      <c r="J56" s="16" t="n"/>
+      <c r="H56" s="15" t="inlineStr">
+        <is>
+          <t>✅ ANSWERED 2026-08-26 (Ralph) — and it is NEITHER of the two options originally posed, nor the sub-office-group option recommended after the FY2027 file was read:
+"For PPDO, the programs will be assigned to the divisions (same as in WFP) for the division of work. And like in WFP they will only see their own division's work. This special filter will not be applied to other offices."
+• PPDO's AIP record is an ORDINARY OFFICE RECORD. No per-division records; NO division column on AipOffice. PPDO's divisions NEVER appear on the printed form — PPDO prints as office rows like any other office.
+• The division lives on the PROGRAM, via the existing ProgramDivision map (v1.2 / RAL-99) — the same mechanism WFP uses. A program may be assigned to MORE THAN ONE division; AllocationService already handles a set.
+• The visibility filter is HOST OFFICE ONLY — it must not apply to ordinary offices.
+⚠️ TWO CONSEQUENCES FOR PHASE 2:
+1. V18-11 is confirmed load-bearing exactly as it predicted — ProgramDivision's (OfficeRefCode, ProgramRefCode) STRING keys are now the sole carrier of PPDO's visibility scoping. Convert to real FKs before Phase 3 builds on it. The original reason for the string keys also lapses: they exist so assignments survive supplemental .xlsm re-uploads, and FY2028+ has no upload.
+2. "Host office only" is NOT enforced anywhere today. WfpService.GetFilteredAsync takes divisionId as a CALLER-SUPPLIED parameter, and OfficeScope.IsHostOfficeUser is used in PermissionService and LandingPageResolver but NOT in WfpService. Building this as an ordinary always-on filter would silently scope EVERY office's AIP by division.</t>
+        </is>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>Ralph</t>
+        </is>
+      </c>
+      <c r="J56" s="16" t="n">
+        <v>46260</v>
+      </c>
       <c r="K56" s="15" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="L56" s="13" t="inlineStr">

--- a/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
+++ b/docs/v1.8/v1.8.0_Open_Items_Tracker.xlsx
@@ -590,6 +590,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -600,10 +601,11 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Every question still blocking or shaping v1.8.0, in one place, with somewhere to write the answer down. Generated 2026-08-25 from docs/v1.8/Monday_Questions.md.</t>
-        </is>
-      </c>
-    </row>
+          <t>Every question still blocking or shaping v1.8.0, in one place, with somewhere to write the answer down. Generated 2026-08-25. (It cited docs/v1.8/Monday_Questions.md, which does NOT exist in the repo — this sheet is the record.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -614,14 +616,14 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Monday_Questions.md — the meeting version, grouped by who can answer</t>
+          <t>⚠ Monday_Questions.md and AIP_Requirements_Review.md are cited here and in Phase_Plan.md but DO NOT EXIST in the repo. Phase_Plan.md is the authoritative source.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>AIP_Requirements_Review.md — the technical reasoning behind each item (§ refs in column L)</t>
+          <t>Phase_Plan.md §12 — the reading of every answer, and what it changed</t>
         </is>
       </c>
     </row>
@@ -656,6 +658,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -705,6 +708,8 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
@@ -733,6 +738,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
@@ -747,6 +753,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
@@ -757,7 +764,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Anything answered here needs recording in AIP_Requirements_Review.md §10 and Phase_Plan.md §9 —</t>
+          <t>Anything answered here needs recording in Phase_Plan.md §9 and §12 —</t>
         </is>
       </c>
     </row>
@@ -768,6 +775,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
